--- a/artfynd/A 48520-2021 artfynd.xlsx
+++ b/artfynd/A 48520-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>118491815</v>
       </c>
       <c r="B2" t="n">
-        <v>94620</v>
+        <v>94627</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 48520-2021 artfynd.xlsx
+++ b/artfynd/A 48520-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -785,6 +785,127 @@
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>103983768</v>
+      </c>
+      <c r="B3" t="n">
+        <v>56921</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Torpsbergen, Srm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>611798</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6548678</v>
+      </c>
+      <c r="S3" t="n">
+        <v>75</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Hyltinge</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2022-10-08</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2022-10-08</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Mats Grling</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Mats Grling</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 48520-2021 artfynd.xlsx
+++ b/artfynd/A 48520-2021 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>103983768</v>
       </c>
       <c r="B3" t="n">
-        <v>56921</v>
+        <v>56925</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,12 +896,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Mats Grling</t>
+          <t>Mats Gärling</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Mats Grling</t>
+          <t>Mats Gärling</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 48520-2021 artfynd.xlsx
+++ b/artfynd/A 48520-2021 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>103983768</v>
       </c>
       <c r="B3" t="n">
-        <v>56925</v>
+        <v>56926</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 48520-2021 artfynd.xlsx
+++ b/artfynd/A 48520-2021 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>103983768</v>
       </c>
       <c r="B3" t="n">
-        <v>56926</v>
+        <v>56927</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 48520-2021 artfynd.xlsx
+++ b/artfynd/A 48520-2021 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>103983768</v>
       </c>
       <c r="B3" t="n">
-        <v>56927</v>
+        <v>56930</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 48520-2021 artfynd.xlsx
+++ b/artfynd/A 48520-2021 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>118491815</v>
       </c>
       <c r="B2" t="n">
-        <v>94629</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +785,7 @@
         <v>103983768</v>
       </c>
       <c r="B3" t="n">
-        <v>56930</v>
+        <v>57141</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -911,11 +906,11 @@
         <v>130977761</v>
       </c>
       <c r="B4" t="n">
-        <v>57834</v>
+        <v>57903</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">

--- a/artfynd/A 48520-2021 artfynd.xlsx
+++ b/artfynd/A 48520-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118491815</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -900,6 +910,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103983768</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1023,8 +1038,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130977761</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>